--- a/docs/FishingFinds-loot.xlsx
+++ b/docs/FishingFinds-loot.xlsx
@@ -2049,7 +2049,7 @@
     <x:t>слишком сильные</x:t>
   </x:si>
   <x:si>
-    <x:t>Handheld Shortwave, записки, ключи, полароиды</x:t>
+    <x:t>Handheld Shortwave, notes, keys, polaroids</x:t>
   </x:si>
   <x:si>
     <x:t>Рация, сюжетные предметы</x:t>
